--- a/survey_templates/034_dietary_restrictions_declaration_form--survey_templates.xlsx
+++ b/survey_templates/034_dietary_restrictions_declaration_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'omnivore'}</t>
+          <t>omnivore</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Omnivore'}</t>
+          <t>Omnivore</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'fish_and_seafood'}</t>
+          <t>fish_and_seafood</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Fish and Seafood'}</t>
+          <t>Fish and Seafood</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'red_meat'}</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Red Meat'}</t>
+          <t>Red Meat</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'poultry'}</t>
+          <t>poultry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Poultry'}</t>
+          <t>Poultry</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'eggs'}</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Eggs'}</t>
+          <t>Eggs</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Dairy'}</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'nuts'}</t>
+          <t>nuts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Nuts'}</t>
+          <t>Nuts</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Soy'}</t>
+          <t>Soy</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'omnivore'}</t>
+          <t>omnivore</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Omnivore'}</t>
+          <t>Omnivore</t>
         </is>
       </c>
     </row>
